--- a/data/trans_dic/KIDM_A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -648,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,57; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,38; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,89; 8,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,09; 6,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,3; 8,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,85; 5,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,92; 4,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,08; 5,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,81; 3,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,88; 5,27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -788,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,12; 5,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,89; 7,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,4; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,36; 3,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,17; 5,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,1; 3,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,96; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,88; 5,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,55; 3,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,13; 2,02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -928,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -996,358 +997,76 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,99; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,45</t>
+          <t>1,68; 5,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,73</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,12</t>
+          <t>0,32; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,46</t>
+          <t>0,89; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,22</t>
+          <t>2,16; 5,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,37</t>
+          <t>0,75; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,37; 3,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,31</t>
+          <t>1,23; 3,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,53</t>
+          <t>2,28; 4,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,52</t>
+          <t>0,99; 2,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,0</t>
+          <t>0,56; 2,45</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 4,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,14; 7,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 3,88</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 3,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 5,29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,06</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 3,38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,97; 3,4</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 5,49</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 3,14</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 2,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 3,9</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,74; 5,21</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 2,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 3,17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 3,47</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 5,77</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 3,47</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 3,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 3,25</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2,42; 4,84</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 2,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
@@ -1356,4 +1075,786 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6969</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9984</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4747</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>790; 7128</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>658; 6376</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>611; 5955</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7813</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3412; 12395</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1394; 8767</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5680</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2114; 9301</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5979; 17040</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2722; 11708</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1476; 8856</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6717</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10742</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1960; 9175</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2882; 11611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>611; 6217</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2066</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>655; 5602</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1924; 8931</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5877</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>170; 5917</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3417; 12166</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5955; 16713</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1726; 9507</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>416; 6374</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20726</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2795; 11970</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4907; 15396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2254; 9348</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>684; 6553</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2687; 10342</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6736; 17923</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2453; 11722</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1015; 8430</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7173; 18806</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13781; 28689</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6434; 16695</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11845</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 5,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,11</t>
+          <t>0,57; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,7</t>
+          <t>0,38; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,66</t>
+          <t>0,9; 8,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,46</t>
+          <t>1,11; 6,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,36</t>
+          <t>2,37; 8,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,35</t>
+          <t>0,84; 5,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,05</t>
+          <t>0,97; 4,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,93</t>
+          <t>2,02; 5,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,48</t>
+          <t>0,96; 3,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,27</t>
+          <t>0,89; 5,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,26</t>
+          <t>1,15; 5,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,6</t>
+          <t>2,21; 7,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,09</t>
+          <t>0,5; 3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,09</t>
+          <t>0,36; 3,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,45</t>
+          <t>1,14; 5,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,41</t>
+          <t>0,09; 3,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,42</t>
+          <t>0,94; 3,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,27</t>
+          <t>2,06; 5,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,03</t>
+          <t>0,52; 2,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,02</t>
+          <t>0,23; 1,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,23</t>
+          <t>0,99; 3,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,27</t>
+          <t>1,87; 5,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,67; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,1</t>
+          <t>0,35; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,42</t>
+          <t>0,83; 3,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,74</t>
+          <t>2,28; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,6</t>
+          <t>0,75; 3,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,09</t>
+          <t>0,38; 3,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,21</t>
+          <t>1,16; 3,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,75</t>
+          <t>2,22; 4,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,57</t>
+          <t>0,91; 2,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,45</t>
+          <t>0,55; 2,58</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4747</t>
+          <t>0; 5450</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>790; 7128</t>
+          <t>792; 7271</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>658; 6376</t>
+          <t>651; 6124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611; 5955</t>
+          <t>619; 6124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1313; 7813</t>
+          <t>1347; 7332</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3412; 12395</t>
+          <t>3511; 12268</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1394; 8767</t>
+          <t>1378; 8268</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5680</t>
+          <t>0; 5026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2114; 9301</t>
+          <t>2228; 10257</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5979; 17040</t>
+          <t>5816; 16289</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2722; 11708</t>
+          <t>3211; 12249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1476; 8856</t>
+          <t>1491; 8908</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1960; 9175</t>
+          <t>2007; 9356</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2882; 11611</t>
+          <t>3382; 11294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>611; 6217</t>
+          <t>754; 6005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>0; 2277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>655; 5602</t>
+          <t>658; 6094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1924; 8931</t>
+          <t>1866; 9395</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5877</t>
+          <t>0; 5986</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>170; 5917</t>
+          <t>164; 6554</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3417; 12166</t>
+          <t>3328; 11623</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5955; 16713</t>
+          <t>6526; 17059</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1726; 9507</t>
+          <t>1621; 8763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>416; 6374</t>
+          <t>716; 6284</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2795; 11970</t>
+          <t>2791; 11054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4907; 15396</t>
+          <t>5479; 16503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2254; 9348</t>
+          <t>2156; 9219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>684; 6553</t>
+          <t>743; 7180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2687; 10342</t>
+          <t>2507; 11529</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6736; 17923</t>
+          <t>7120; 17336</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2453; 11722</t>
+          <t>2438; 11252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1015; 8430</t>
+          <t>1033; 9551</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7173; 18806</t>
+          <t>6774; 17910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13781; 28689</t>
+          <t>13409; 28347</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6434; 16695</t>
+          <t>5896; 16314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2712; 11845</t>
+          <t>2673; 12489</t>
         </is>
       </c>
     </row>
